--- a/Keyboard BOM.xlsx
+++ b/Keyboard BOM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ac8f2ab3c324b6b/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ac8f2ab3c324b6b/Documents/GitHub/Crazy-75/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{FCCC2E56-FDB1-4E02-ACF6-F81B5EFE9B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{841789F6-15C5-4F11-9AB4-76034AC9DC02}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{FCCC2E56-FDB1-4E02-ACF6-F81B5EFE9B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6456961-AF34-4CCE-BF8D-AF1B39CD61EA}"/>
   <bookViews>
-    <workbookView xWindow="12180" yWindow="2685" windowWidth="27300" windowHeight="15300" xr2:uid="{7E7D5457-AF9F-4A24-AB89-FCDAB66E2EA5}"/>
+    <workbookView xWindow="23100" yWindow="2595" windowWidth="27300" windowHeight="15300" xr2:uid="{7E7D5457-AF9F-4A24-AB89-FCDAB66E2EA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>Part No.</t>
   </si>
@@ -60,6 +60,24 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>.</t>
+  </si>
+  <si>
+    <t>0.08/pc</t>
+  </si>
+  <si>
+    <t>1x100pcs</t>
+  </si>
+  <si>
+    <t>Kailh Hot Plug Base</t>
+  </si>
+  <si>
+    <t>Kailh Hot-swappable PCB socket Hot Plug CPG151101S11 for Gateron Outemu Cherry MX Switches Mechanical Keyboard DIY wholesale</t>
+  </si>
+  <si>
+    <t>https://fr.aliexpress.com/item/1005006105603269.html?spm=a2g0n.productlist.0.0.3858BhLlBhLlik&amp;browser_id=2269fcae49994bc495ac18d9a18a9643&amp;aff_trace_key=a9b6c8e739aa4a98a2d8e403b501ff28-1780918887469-07997-_DFhInr9&amp;aff_platform=msite&amp;m_page_id=v5mtilbuikgcav781a01db52ac211d721d5c185afe&amp;gclid=&amp;pdp_ext_f=%7B%22order%22%3A%22227%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%217.05%215.84%21%21%218.04%216.66%21%400b15834e17872048241487926e0cff%2112000035768903525%21sea%21LU%218155715332%21X%211%210%21n_tag%3A-29911%3Bd%3A5b165265%3Bm03_new_user%3A-29895%3BpisId%3A5000000215237127&amp;algo_pvid=b39dc535-db3c-4a87-95d6-ba503a4c97bf&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006105603269%7C_p_origin_prod%3A</t>
   </si>
 </sst>
 </file>
@@ -431,16 +449,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5F0154-0866-430C-ACD5-87E79D9222E2}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
     <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -462,30 +482,66 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>7.91</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="H4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
+      </c>
+      <c r="H6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/Keyboard BOM.xlsx
+++ b/Keyboard BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5ac8f2ab3c324b6b/Documents/GitHub/Crazy-75/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{FCCC2E56-FDB1-4E02-ACF6-F81B5EFE9B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6456961-AF34-4CCE-BF8D-AF1B39CD61EA}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{FCCC2E56-FDB1-4E02-ACF6-F81B5EFE9B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CFAD482-735E-48B7-B9AF-92B7D55F0986}"/>
   <bookViews>
-    <workbookView xWindow="23100" yWindow="2595" windowWidth="27300" windowHeight="15300" xr2:uid="{7E7D5457-AF9F-4A24-AB89-FCDAB66E2EA5}"/>
+    <workbookView xWindow="31590" yWindow="4035" windowWidth="27300" windowHeight="15300" xr2:uid="{7E7D5457-AF9F-4A24-AB89-FCDAB66E2EA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="29">
   <si>
     <t>Part No.</t>
   </si>
@@ -78,6 +78,54 @@
   </si>
   <si>
     <t>https://fr.aliexpress.com/item/1005006105603269.html?spm=a2g0n.productlist.0.0.3858BhLlBhLlik&amp;browser_id=2269fcae49994bc495ac18d9a18a9643&amp;aff_trace_key=a9b6c8e739aa4a98a2d8e403b501ff28-1780918887469-07997-_DFhInr9&amp;aff_platform=msite&amp;m_page_id=v5mtilbuikgcav781a01db52ac211d721d5c185afe&amp;gclid=&amp;pdp_ext_f=%7B%22order%22%3A%22227%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%217.05%215.84%21%21%218.04%216.66%21%400b15834e17872048241487926e0cff%2112000035768903525%21sea%21LU%218155715332%21X%211%210%21n_tag%3A-29911%3Bd%3A5b165265%3Bm03_new_user%3A-29895%3BpisId%3A5000000215237127&amp;algo_pvid=b39dc535-db3c-4a87-95d6-ba503a4c97bf&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006105603269%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://fr.aliexpress.com/item/1005002339916163.html?spm=a2g0o.productlist.main.2.46c81132SHFxiA&amp;algo_pvid=a83b4908-b404-4225-bb7f-e63c043536a8&amp;algo_exp_id=a83b4908-b404-4225-bb7f-e63c043536a8-1&amp;pdp_ext_f=%7B%22order%22%3A%221217%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%210.95%210.80%21%21%211.08%210.91%21%402141396c17877644236763187e0e9b%2112000020175180916%21sea%21LU%218155715332%21X%211%210%21n_tag%3A-29911%3Bd%3Ae8fc6401%3Bm03_new_user%3A-29895&amp;curPageLogUid=At9t6Io5QElN&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005002339916163%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>1N4148 High-speed Switching Diodes</t>
+  </si>
+  <si>
+    <t>https://fr.aliexpress.com/item/1005007863635868.html?spm=a2g0o.productlist.main.1.4e9b287euWBh5L&amp;algo_pvid=500774f2-fd0a-4dd4-94a0-28eb4fd5b955&amp;algo_exp_id=500774f2-fd0a-4dd4-94a0-28eb4fd5b955-0&amp;pdp_ext_f=%7B%22order%22%3A%22608%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%214.35%214.35%21%21%214.96%214.96%21%400bafc98f17877647154796069e0c19%2112000042594617264%21sea%21LU%218155715332%21X%211%210%21n_tag%3A-29911%3Bd%3Ae8fc6401%3Bm03_new_user%3A-29895&amp;curPageLogUid=OsdDD2ovEBL6&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007863635868%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>SK6812 MINI-E RGB</t>
+  </si>
+  <si>
+    <t>https://fr.aliexpress.com/item/1005007644083514.html?spm=a2g0o.productlist.main.1.29107465rbQVG8&amp;algo_pvid=4e65f76f-b2a6-4e8a-9c6c-c0efcc68cab4&amp;algo_exp_id=4e65f76f-b2a6-4e8a-9c6c-c0efcc68cab4-0&amp;pdp_ext_f=%7B%22order%22%3A%224230%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%211.68%211.66%21%21%211.91%211.89%21%402141397017877649553981636e0d97%2112000041630839409%21sea%21LU%218155715332%21X%211%210%21n_tag%3A-29911%3Bd%3Ae8fc6401%3Bm03_new_user%3A-29895&amp;curPageLogUid=RiI44SzlN0mT&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007644083514%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>360 Degree Rotary Encoder EC11 With Push Button</t>
+  </si>
+  <si>
+    <t>EC11</t>
+  </si>
+  <si>
+    <t>1pc</t>
+  </si>
+  <si>
+    <t>https://fr.aliexpress.com/item/1005007369669431.html?spm=a2g0o.productlist.main.3.193201TR01TR1P&amp;algo_pvid=1936a5f8-4955-4ddf-ab19-5181f7e135f5&amp;algo_exp_id=1936a5f8-4955-4ddf-ab19-5181f7e135f5-2&amp;pdp_ext_f=%7B%22order%22%3A%22764%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%212.75%212.75%21%21%213.14%213.14%21%400be71e1e17877677506374984e0f30%2112000040462155655%21sea%21LU%218155715332%21X%211%210%21n_tag%3A-29911%3Bd%3Ae8fc6401%3Bm03_new_user%3A-29895&amp;curPageLogUid=LZYu56IlV2lS&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007369669431%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>RP2040 Raspberry Pi Pico-compatible, standard 40-pin / 21 × 51 mm footprint</t>
+  </si>
+  <si>
+    <t>Pico clone</t>
+  </si>
+  <si>
+    <t>Switches</t>
+  </si>
+  <si>
+    <t>Keycaps</t>
+  </si>
+  <si>
+    <t>https://fr.aliexpress.com/item/1005001831944910.html?spm=a2g0o.productlist.main.40.47a54f83nepaIs&amp;algo_pvid=24cc262e-6fc1-4a7e-a60e-4fd43e9bc0c5&amp;algo_exp_id=24cc262e-6fc1-4a7e-a60e-4fd43e9bc0c5-37&amp;pdp_ext_f=%7B%22order%22%3A%2249%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21EUR%216.40%215.73%21%21%217.29%216.53%21%402102ee9117877651642787783e0eae%2112000017788498378%21sea%21LU%218155715332%21X%211%210%21n_tag%3A-29911%3Bd%3Ae8fc6401%3Bm03_new_user%3A-29895&amp;curPageLogUid=IgHeZ4W9rER0&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005001831944910%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>Stabilizers</t>
+  </si>
+  <si>
+    <t>6.25u &amp; 4x2u</t>
   </si>
 </sst>
 </file>
@@ -130,6 +178,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -449,14 +501,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F5F0154-0866-430C-ACD5-87E79D9222E2}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" customWidth="1"/>
     <col min="7" max="7" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -516,6 +568,9 @@
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
       <c r="H3" t="s">
         <v>7</v>
       </c>
@@ -524,6 +579,9 @@
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
       <c r="H4" t="s">
         <v>7</v>
       </c>
@@ -532,6 +590,18 @@
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5">
+        <v>0.8</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
       <c r="H5" t="s">
         <v>7</v>
       </c>
@@ -540,11 +610,103 @@
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
       <c r="H6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
+        <v>1.66</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>3.36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9">
+        <v>5.73</v>
+      </c>
+      <c r="G9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>